--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="239">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -413,7 +413,32 @@
 </t>
   </si>
   <si>
+    <t>Date et heure de la prise de responsabilité</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.time.nullFlavor</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.time.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime {http://hl7.org/cda/stds/core/StructureDefinition/ts-simple}
+</t>
+  </si>
+  <si>
+    <t>Date et heure de la prise de responsabilité précisée à la seconde avec précision du décalage par rapport au temps universel (UTC)</t>
+  </si>
+  <si>
+    <t>A quantity specifying a point on the axis of natural time. A point in time is most often represented as a calendar expression.</t>
+  </si>
+  <si>
+    <t>TS.value</t>
+  </si>
+  <si>
     <t>LegalAuthenticator.signatureCode</t>
+  </si>
+  <si>
+    <t>Signature</t>
   </si>
   <si>
     <t>http://hl7.org/cda/stds/core/ValueSet/CDASignatureCode</t>
@@ -423,21 +448,310 @@
 </t>
   </si>
   <si>
-    <t>LegalAuthenticator.sdtcSignatureText</t>
+    <t>LegalAuthenticator.signatureCode.nullFlavor</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.signatureCode.code</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.signatureCode.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.signatureCode.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.signatureCode.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.signatureCode.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.signatureCode.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.signatureCode.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.signatureCode.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
 </t>
   </si>
   <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.signatureCode.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.signatureCode.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CD
+</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.sdtcSignatureText</t>
+  </si>
+  <si>
     <t>A textual or multimedia depiction of the signature by which the participant endorses his or her participation in the Act as specified in the Participation.typeCode and that he or she agrees to assume the associated accountability.</t>
   </si>
   <si>
     <t>LegalAuthenticator.assignedEntity</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AssignedEntity
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AssignedEntity {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-assigned-entity}
 </t>
+  </si>
+  <si>
+    <t>Responsable du document</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.nullFlavor</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.realmCode</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.typeId</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.typeId.displayable</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.typeId.root</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.typeId.extension</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.templateId</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.classCode</t>
+  </si>
+  <si>
+    <t>ASSIGNED</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-RoleClassAssignedEntity</t>
+  </si>
+  <si>
+    <t>AssignedEntity.classCode</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.id</t>
+  </si>
+  <si>
+    <t>AssignedEntity.id</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.sdtcIdentifiedBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IdentifiedBy
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcIdentifiedBy</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
+</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
+  </si>
+  <si>
+    <t>AssignedEntity.code</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.code.code</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.code.codeSystem</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.code.displayName</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.code.originalText</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.code.qualifier</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.code.translation</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.addr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AD
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.addr</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/TEL
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.telecom</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.assignedPerson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Person {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-person}
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.assignedPerson</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.representedOrganization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.representedOrganization</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.sdtcPatient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcPatient</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.sdtcPatient.id</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcPatient.id</t>
   </si>
 </sst>
 </file>
@@ -739,11 +1053,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK17"/>
+  <dimension ref="A1:AK60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.09375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.09375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="62.19140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="62.19140625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
@@ -767,13 +1081,13 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.46484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="97.74609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="37.41796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.20703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1014,7 +1328,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>74</v>
@@ -1317,7 +1631,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1418,7 +1732,7 @@
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1521,7 +1835,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1929,7 +2243,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2026,7 +2340,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -2137,7 +2451,9 @@
       <c r="K14" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="L14" s="2"/>
+      <c r="L14" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2208,18 +2524,20 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F15" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>75</v>
@@ -2234,10 +2552,12 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="M15" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2267,7 +2587,7 @@
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2285,10 +2605,10 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>75</v>
@@ -2297,7 +2617,7 @@
         <v>74</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>74</v>
@@ -2305,10 +2625,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2331,9 +2651,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
         <v>135</v>
       </c>
@@ -2386,7 +2708,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2406,10 +2728,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2432,9 +2754,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L17" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2461,13 +2785,11 @@
         <v>74</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>74</v>
@@ -2485,7 +2807,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -2497,9 +2819,4370 @@
         <v>74</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y18" s="2"/>
+      <c r="Z18" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L25" s="2"/>
+      <c r="M25" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L31" s="2"/>
+      <c r="M31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y31" s="2"/>
+      <c r="Z31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y34" s="2"/>
+      <c r="Z34" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L39" s="2"/>
+      <c r="M39" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y40" s="2"/>
+      <c r="Z40" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y43" s="2"/>
+      <c r="Z43" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y44" s="2"/>
+      <c r="Z44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L45" s="2"/>
+      <c r="M45" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L46" s="2"/>
+      <c r="M46" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L47" s="2"/>
+      <c r="M47" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L48" s="2"/>
+      <c r="M48" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L49" s="2"/>
+      <c r="M49" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L50" s="2"/>
+      <c r="M50" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L51" s="2"/>
+      <c r="M51" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L52" s="2"/>
+      <c r="M52" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L53" s="2"/>
+      <c r="M53" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L54" s="2"/>
+      <c r="M54" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK60" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1913" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="238">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -438,7 +438,7 @@
     <t>LegalAuthenticator.signatureCode</t>
   </si>
   <si>
-    <t>Signature</t>
+    <t>signatureCode confirme la prise la responsabilité du document.</t>
   </si>
   <si>
     <t>http://hl7.org/cda/stds/core/ValueSet/CDASignatureCode</t>
@@ -452,9 +452,6 @@
   </si>
   <si>
     <t>LegalAuthenticator.signatureCode.code</t>
-  </si>
-  <si>
-    <t>S</t>
   </si>
   <si>
     <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
@@ -2958,11 +2955,9 @@
       <c r="K19" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="L19" s="2"/>
+      <c r="M19" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3013,7 +3008,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3033,17 +3028,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -3065,7 +3060,7 @@
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3116,7 +3111,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3136,17 +3131,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>80</v>
@@ -3168,7 +3163,7 @@
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3219,7 +3214,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3239,17 +3234,17 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>80</v>
@@ -3271,7 +3266,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3322,7 +3317,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3342,17 +3337,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>80</v>
@@ -3374,7 +3369,7 @@
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3425,7 +3420,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3445,10 +3440,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3471,11 +3466,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3526,7 +3521,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3546,10 +3541,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3576,7 +3571,7 @@
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3627,7 +3622,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3647,39 +3642,39 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K26" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="F26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K26" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3730,7 +3725,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3750,39 +3745,39 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="F27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3833,7 +3828,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3853,39 +3848,39 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E28" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="F28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K28" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3936,7 +3931,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3956,10 +3951,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3982,11 +3977,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4037,7 +4032,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4057,10 +4052,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4083,10 +4078,10 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -4138,7 +4133,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4158,10 +4153,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4259,10 +4254,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4360,10 +4355,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4461,10 +4456,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4562,10 +4557,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4665,10 +4660,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4768,10 +4763,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4871,10 +4866,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4974,10 +4969,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5075,10 +5070,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5112,7 +5107,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>74</v>
@@ -5134,25 +5129,25 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5172,10 +5167,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5251,7 +5246,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5271,10 +5266,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5297,7 +5292,7 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -5350,7 +5345,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5370,10 +5365,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5396,7 +5391,7 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -5429,25 +5424,25 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5467,10 +5462,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5568,10 +5563,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5600,7 +5595,7 @@
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5651,7 +5646,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5671,17 +5666,17 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>80</v>
@@ -5703,7 +5698,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5754,7 +5749,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5774,17 +5769,17 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>80</v>
@@ -5806,7 +5801,7 @@
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5857,7 +5852,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -5877,17 +5872,17 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>80</v>
@@ -5909,7 +5904,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5960,7 +5955,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -5980,17 +5975,17 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
@@ -6012,7 +6007,7 @@
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6063,7 +6058,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6083,10 +6078,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6109,11 +6104,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6164,7 +6159,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6184,10 +6179,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6214,7 +6209,7 @@
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6265,7 +6260,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6285,39 +6280,39 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K52" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="F52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6368,7 +6363,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6388,39 +6383,39 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K53" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="F53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6471,7 +6466,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6491,17 +6486,17 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>80</v>
@@ -6519,11 +6514,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6574,7 +6569,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6594,10 +6589,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6620,7 +6615,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -6673,7 +6668,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6693,10 +6688,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6719,7 +6714,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -6772,7 +6767,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -6792,10 +6787,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6818,7 +6813,7 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -6871,7 +6866,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -6891,10 +6886,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -6917,7 +6912,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -6970,7 +6965,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -6990,10 +6985,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7016,7 +7011,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7069,7 +7064,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7089,10 +7084,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7168,7 +7163,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="247">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,6 +313,10 @@
     <t>InfrastructureRoot.typeId</t>
   </si>
   <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
+  </si>
+  <si>
     <t>LegalAuthenticator.typeId.nullFlavor</t>
   </si>
   <si>
@@ -637,6 +641,34 @@
   </si>
   <si>
     <t>AssignedEntity.id</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.id.nullFlavor</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.id.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.id.displayable</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.id.root</t>
+  </si>
+  <si>
+    <t>- Pour un professionnel : '1.2.250.1.71.4.2.1'
+- Pour le patient/usager : OID de l'autorité d'affectation de l'INS
+- Pour un système de structure : '1.2.250.1.71.4.2.1' 
+- Pour un SNR : OID de l'éditeur 
+- Pour le DP : '1.2.250.1.71.4.2.1'</t>
+  </si>
+  <si>
+    <t>A unique identifier that guarantees the global uniqueness of the instance identifier. The root alone may be the entire instance identifier.</t>
+  </si>
+  <si>
+    <t>LegalAuthenticator.assignedEntity.id.extension</t>
+  </si>
+  <si>
+    <t>Valeur de l’identifiant</t>
   </si>
   <si>
     <t>LegalAuthenticator.assignedEntity.sdtcIdentifiedBy</t>
@@ -1050,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK60"/>
+  <dimension ref="A1:AK65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.19140625" customWidth="true" bestFit="true"/>
@@ -1604,7 +1636,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1612,10 +1644,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1713,17 +1745,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1741,11 +1773,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1796,7 +1828,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1816,17 +1848,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1844,11 +1876,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1899,7 +1931,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1919,17 +1951,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1947,11 +1979,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1960,7 +1992,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -2002,7 +2034,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2022,17 +2054,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -2050,11 +2082,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2105,7 +2137,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2125,10 +2157,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2155,7 +2187,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2206,7 +2238,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2226,10 +2258,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2263,7 +2295,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2285,7 +2317,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2303,7 +2335,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2323,10 +2355,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2360,7 +2392,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2382,7 +2414,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2400,7 +2432,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2420,10 +2452,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2446,10 +2478,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2501,7 +2533,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2521,10 +2553,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2622,10 +2654,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2648,13 +2680,13 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2705,7 +2737,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2725,10 +2757,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2754,7 +2786,7 @@
         <v>91</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -2786,7 +2818,7 @@
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>74</v>
@@ -2804,7 +2836,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -2816,7 +2848,7 @@
         <v>74</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>74</v>
@@ -2824,10 +2856,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2925,10 +2957,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2957,7 +2989,7 @@
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3008,7 +3040,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3028,17 +3060,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -3056,11 +3088,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3111,7 +3143,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3131,17 +3163,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>80</v>
@@ -3159,11 +3191,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3214,7 +3246,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3234,17 +3266,17 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>80</v>
@@ -3262,11 +3294,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3317,7 +3349,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3337,17 +3369,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>80</v>
@@ -3365,11 +3397,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3420,7 +3452,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3440,10 +3472,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3466,11 +3498,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3521,7 +3553,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3541,10 +3573,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3567,11 +3599,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3622,7 +3654,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3642,17 +3674,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3670,11 +3702,11 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3725,7 +3757,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3745,17 +3777,17 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
@@ -3773,11 +3805,11 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3828,7 +3860,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3848,17 +3880,17 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>80</v>
@@ -3876,11 +3908,11 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3931,7 +3963,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3951,10 +3983,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3977,11 +4009,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4032,7 +4064,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4052,10 +4084,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4078,10 +4110,10 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -4133,7 +4165,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4153,10 +4185,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4254,10 +4286,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4355,10 +4387,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4448,7 +4480,7 @@
         <v>74</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>74</v>
@@ -4456,10 +4488,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4557,17 +4589,17 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>80</v>
@@ -4585,11 +4617,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4640,7 +4672,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4660,17 +4692,17 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
@@ -4688,11 +4720,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4743,7 +4775,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4763,17 +4795,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>75</v>
@@ -4791,11 +4823,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4804,7 +4836,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>74</v>
@@ -4846,7 +4878,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4866,17 +4898,17 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>75</v>
@@ -4894,11 +4926,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4949,7 +4981,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -4969,10 +5001,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4999,7 +5031,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5050,7 +5082,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5070,10 +5102,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5107,7 +5139,7 @@
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>74</v>
@@ -5129,7 +5161,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>74</v>
@@ -5147,7 +5179,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5167,10 +5199,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5246,7 +5278,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5266,16 +5298,18 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
@@ -5292,10 +5326,12 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>204</v>
+        <v>85</v>
       </c>
       <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
+      <c r="M42" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5321,13 +5357,11 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -5345,13 +5379,13 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>205</v>
+        <v>89</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>74</v>
@@ -5365,21 +5399,23 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>74</v>
@@ -5391,10 +5427,12 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>207</v>
+        <v>102</v>
       </c>
       <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
+      <c r="M43" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5420,11 +5458,13 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>208</v>
+        <v>74</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5442,7 +5482,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>209</v>
+        <v>104</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5462,17 +5502,17 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5490,11 +5530,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5521,11 +5561,13 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>74</v>
@@ -5543,7 +5585,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5563,20 +5605,20 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>75</v>
@@ -5591,11 +5633,13 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L45" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="M45" t="s" s="2">
-        <v>143</v>
+        <v>209</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5646,7 +5690,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5666,20 +5710,20 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>75</v>
@@ -5694,11 +5738,13 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L46" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="M46" t="s" s="2">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5749,7 +5795,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5769,23 +5815,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>74</v>
@@ -5797,12 +5841,10 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>101</v>
+        <v>213</v>
       </c>
       <c r="L47" s="2"/>
-      <c r="M47" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -5852,13 +5894,13 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>74</v>
@@ -5872,23 +5914,21 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E48" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>74</v>
@@ -5900,12 +5940,10 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>101</v>
+        <v>216</v>
       </c>
       <c r="L48" s="2"/>
-      <c r="M48" t="s" s="2">
-        <v>155</v>
-      </c>
+      <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -5931,13 +5969,11 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>74</v>
+        <v>217</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -5955,7 +5991,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>156</v>
+        <v>218</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -5975,23 +6011,23 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>74</v>
@@ -6003,11 +6039,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6034,13 +6070,11 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6058,7 +6092,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6078,21 +6112,23 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E50" s="2"/>
+      <c r="E50" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>74</v>
@@ -6104,11 +6140,11 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>162</v>
+        <v>85</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6159,7 +6195,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6179,21 +6215,23 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>74</v>
@@ -6205,11 +6243,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6260,7 +6298,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6280,17 +6318,17 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
@@ -6308,11 +6346,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6363,7 +6401,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6383,17 +6421,17 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>80</v>
@@ -6411,11 +6449,11 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6466,13 +6504,13 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>74</v>
@@ -6486,23 +6524,23 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>74</v>
@@ -6514,11 +6552,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6569,13 +6607,13 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>74</v>
@@ -6589,10 +6627,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6603,7 +6641,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>74</v>
@@ -6615,10 +6653,12 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>222</v>
+        <v>163</v>
       </c>
       <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
+      <c r="M55" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -6668,13 +6708,13 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>223</v>
+        <v>165</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>74</v>
@@ -6688,10 +6728,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6702,7 +6742,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>74</v>
@@ -6714,10 +6754,12 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>225</v>
+        <v>102</v>
       </c>
       <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
+      <c r="M56" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -6767,13 +6809,13 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>74</v>
@@ -6796,7 +6838,9 @@
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
@@ -6813,10 +6857,12 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
+      <c r="M57" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -6866,7 +6912,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>229</v>
+        <v>173</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -6886,21 +6932,23 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E58" s="2"/>
+      <c r="E58" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>74</v>
@@ -6912,10 +6960,12 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
+      <c r="M58" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -6965,13 +7015,13 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>232</v>
+        <v>178</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>74</v>
@@ -6985,21 +7035,23 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E59" s="2"/>
+      <c r="E59" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>74</v>
@@ -7011,10 +7063,12 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>234</v>
+        <v>181</v>
       </c>
       <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
+      <c r="M59" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7064,13 +7118,13 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>235</v>
+        <v>183</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>74</v>
@@ -7084,10 +7138,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7095,10 +7149,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>74</v>
@@ -7110,7 +7164,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>95</v>
+        <v>231</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7163,21 +7217,516 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K62" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AG60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK60" t="s" s="2">
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK65" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="253">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -638,6 +638,9 @@
   </si>
   <si>
     <t>LegalAuthenticator.assignedEntity.id</t>
+  </si>
+  <si>
+    <t>Identifiant du responsable</t>
   </si>
   <si>
     <t>AssignedEntity.id</t>
@@ -668,7 +671,9 @@
     <t>LegalAuthenticator.assignedEntity.id.extension</t>
   </si>
   <si>
-    <t>Valeur de l’identifiant</t>
+    <t>Valeur de l’identifiant.
+- Pour le PS, valeur de PS_IdNat (voir CI-SIS_ANX_SOURCES-DONNEES-PERSONNES-STRUCTURES).
+- Pour le patient/usager, valeur de l'INS du patient/usager.</t>
   </si>
   <si>
     <t>LegalAuthenticator.assignedEntity.sdtcIdentifiedBy</t>
@@ -688,6 +693,9 @@
 </t>
   </si>
   <si>
+    <t>Profession ou rôle du responsable</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
   </si>
   <si>
@@ -734,6 +742,9 @@
 </t>
   </si>
   <si>
+    <t>Adresse géopostale</t>
+  </si>
+  <si>
     <t>AssignedEntity.addr</t>
   </si>
   <si>
@@ -744,6 +755,9 @@
 </t>
   </si>
   <si>
+    <t>Coordonnées télécom</t>
+  </si>
+  <si>
     <t>AssignedEntity.telecom</t>
   </si>
   <si>
@@ -754,6 +768,13 @@
 </t>
   </si>
   <si>
+    <t>Personne physique : 
+- Obligatoire pour un professionnel 
+- Obligatoire pour un patient/usager 
+- Non utilisé pour un SNR 
+- Non utilisé pour le DP</t>
+  </si>
+  <si>
     <t>AssignedEntity.assignedPerson</t>
   </si>
   <si>
@@ -762,6 +783,11 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
 </t>
+  </si>
+  <si>
+    <t>Structure de rattachement :
+- Pour un PS : Organisation pour le compte de laquelle intervient le PS.
+- Pour un patient : seul l'élément standardIndustryClassCode est renseigné (cas particulier des documents d'expression personnelle du patient).</t>
   </si>
   <si>
     <t>AssignedEntity.representedOrganization</t>
@@ -5227,7 +5253,9 @@
       <c r="K41" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L41" s="2"/>
+      <c r="L41" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5278,7 +5306,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5298,10 +5326,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5399,10 +5427,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5502,10 +5530,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5605,10 +5633,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5636,10 +5664,10 @@
         <v>112</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5710,10 +5738,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5741,7 +5769,7 @@
         <v>102</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>118</v>
@@ -5815,10 +5843,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5841,7 +5869,7 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -5894,7 +5922,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -5914,10 +5942,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5940,9 +5968,11 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="L48" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5973,7 +6003,7 @@
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -5991,7 +6021,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6011,10 +6041,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6112,10 +6142,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6215,10 +6245,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6318,10 +6348,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6421,10 +6451,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6524,10 +6554,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6627,10 +6657,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6728,10 +6758,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6829,10 +6859,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6932,10 +6962,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7035,10 +7065,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7138,10 +7168,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7164,9 +7194,11 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="L60" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7217,7 +7249,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7237,10 +7269,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7263,9 +7295,11 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="L61" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7316,7 +7350,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7336,10 +7370,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7362,9 +7396,11 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="L62" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7415,7 +7451,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7435,10 +7471,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7461,9 +7497,11 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="L63" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7514,7 +7552,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7534,10 +7572,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7560,7 +7598,7 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -7613,7 +7651,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7633,10 +7671,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7712,7 +7750,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>LegalAuthenticator représente les caractéristiques du professionnel et/ou de l'établissement participant.</t>
+    <t>L'élément de l'en-tête du CDA legalAuthenticator permet de représenter les caractéristiques du professionnel et/ou de l'établissement participant.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-legal-authenticator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
